--- a/files/FIN_Trial_Balance.xlsx
+++ b/files/FIN_Trial_Balance.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trial Balance" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,19 +26,26 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Aptos"/>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001F4E78"/>
-      <sz val="14"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="16"/>
     </font>
     <font>
-      <name val="Aptos"/>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="006B7280"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
-      <name val="Aptos"/>
+      <name val="Calibri"/>
+      <color rgb="00222222"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -51,12 +58,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
+        <fgColor rgb="001F2D55"/>
+        <bgColor rgb="001F2D55"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00F4F6FB"/>
+        <bgColor rgb="00F4F6FB"/>
       </patternFill>
     </fill>
   </fills>
@@ -70,30 +79,45 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D0D7DE"/>
+        <color rgb="00D0D7E2"/>
       </left>
       <right style="thin">
-        <color rgb="00D0D7DE"/>
+        <color rgb="00D0D7E2"/>
       </right>
       <top style="thin">
-        <color rgb="00D0D7DE"/>
+        <color rgb="00D0D7E2"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D0D7DE"/>
+        <color rgb="00D0D7E2"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -459,513 +483,1089 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Zava Group - Trial Balance as at 30-Apr-2026 (MYR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Account</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Credit</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
+          <t>FIN Trial Balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Source file: FIN_Trial_Balance.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>Period</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Cash - KL Operating</t>
+          <t>Opening</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Drawdown</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>28,400,000</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr"/>
+          <t>Interest</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Repayment</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Closing</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>1010</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Cash - SGD Hedge</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>12,800,000</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr"/>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>162278759</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>162278758.6376841</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>913351</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>2704646</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>3617997</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>159574113</v>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Initial drawdown</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>1100</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Trade receivables</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>184,200,000</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr"/>
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>159574113</v>
+      </c>
+      <c r="C6" s="6" t="inlineStr"/>
+      <c r="D6" s="7" t="n">
+        <v>898128</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>2704646</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>3602774</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>156869467</v>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Inventory - finished</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>67,800,000</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr"/>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>156869467</v>
+      </c>
+      <c r="C7" s="4" t="inlineStr"/>
+      <c r="D7" s="5" t="n">
+        <v>882906</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>2704646</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>3587552</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>154164821</v>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>1500</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>PPE - Buildings</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>412,300,000</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr"/>
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>154164821</v>
+      </c>
+      <c r="C8" s="6" t="inlineStr"/>
+      <c r="D8" s="7" t="n">
+        <v>867683</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>2704646</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>3572329</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>151460175</v>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>1510</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>PPE - Plant</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>278,900,000</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr"/>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>151460175</v>
+      </c>
+      <c r="C9" s="4" t="inlineStr"/>
+      <c r="D9" s="5" t="n">
+        <v>852461</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>2704646</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>3557107</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>148755529</v>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Trade payables</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Liability</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr"/>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>142,500,000</t>
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>148755529</v>
+      </c>
+      <c r="C10" s="6" t="inlineStr"/>
+      <c r="D10" s="7" t="n">
+        <v>837238</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>2704646</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>3541884</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>146050883</v>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2100</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Short-term debt</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Liability</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr"/>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>88,400,000</t>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>146050883</v>
+      </c>
+      <c r="C11" s="4" t="inlineStr"/>
+      <c r="D11" s="5" t="n">
+        <v>822016</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>2704646</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>3526662</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>143346237</v>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>2200</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Long-term debt</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Liability</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr"/>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>412,700,000</t>
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>143346237</v>
+      </c>
+      <c r="C12" s="6" t="inlineStr"/>
+      <c r="D12" s="7" t="n">
+        <v>806793</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>2704646</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>3511439</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>140641591</v>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>3000</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Share capital</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr"/>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>250,000,000</t>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>140641591</v>
+      </c>
+      <c r="C13" s="4" t="inlineStr"/>
+      <c r="D13" s="5" t="n">
+        <v>791571</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>2704646</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>3496217</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>137936945</v>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>3100</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Retained earnings</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr"/>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>224,300,000</t>
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n">
+        <v>137936945</v>
+      </c>
+      <c r="C14" s="6" t="inlineStr"/>
+      <c r="D14" s="7" t="n">
+        <v>776348</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>2704646</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>3480994</v>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>135232299</v>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Revenue - Banking</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr"/>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>1,842,000,000</t>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>135232299</v>
+      </c>
+      <c r="C15" s="4" t="inlineStr"/>
+      <c r="D15" s="5" t="n">
+        <v>761126</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>2704646</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>3465772</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>132527653</v>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>4010</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Revenue - Insurance</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr"/>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>928,400,000</t>
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>132527653</v>
+      </c>
+      <c r="C16" s="6" t="inlineStr"/>
+      <c r="D16" s="7" t="n">
+        <v>745903</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>2704646</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>3450549</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>129823007</v>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>4020</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Revenue - Property</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr"/>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>612,800,000</t>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>129823007</v>
+      </c>
+      <c r="C17" s="4" t="inlineStr"/>
+      <c r="D17" s="5" t="n">
+        <v>730681</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>2704646</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>3435327</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>127118361</v>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>COGS</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>1,424,300,000</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr"/>
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>2027-01</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n">
+        <v>127118361</v>
+      </c>
+      <c r="C18" s="6" t="inlineStr"/>
+      <c r="D18" s="7" t="n">
+        <v>715458</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>2704646</v>
+      </c>
+      <c r="F18" s="7" t="n">
+        <v>3420104</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>124413715</v>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>6000</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Opex - Personnel</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>312,400,000</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr"/>
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>124413715</v>
+      </c>
+      <c r="C19" s="4" t="inlineStr"/>
+      <c r="D19" s="5" t="n">
+        <v>700236</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>2704646</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>3404881</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>121709069</v>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>6100</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Opex - Selling</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>142,800,000</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr"/>
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>2027-04</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n">
+        <v>121709069</v>
+      </c>
+      <c r="C20" s="6" t="inlineStr"/>
+      <c r="D20" s="7" t="n">
+        <v>685013</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>2704646</v>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>3389659</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>119004423</v>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>6200</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Opex - G&amp;A</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>88,300,000</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr"/>
+          <t>2027-05</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>119004423</v>
+      </c>
+      <c r="C21" s="4" t="inlineStr"/>
+      <c r="D21" s="5" t="n">
+        <v>669790</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>2704646</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>3374436</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>116299777</v>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>7000</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Finance cost</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>84,700,000</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr"/>
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>2027-06</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="n">
+        <v>116299777</v>
+      </c>
+      <c r="C22" s="6" t="inlineStr"/>
+      <c r="D22" s="7" t="n">
+        <v>654568</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>2704646</v>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>3359214</v>
+      </c>
+      <c r="G22" s="7" t="n">
+        <v>113595131</v>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>8000</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Tax expense</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>42,300,000</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr"/>
+          <t>2027-07</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>113595131</v>
+      </c>
+      <c r="C23" s="4" t="inlineStr"/>
+      <c r="D23" s="5" t="n">
+        <v>639345</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>2704646</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>3343991</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>110890485</v>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>2027-08</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="n">
+        <v>110890485</v>
+      </c>
+      <c r="C24" s="6" t="inlineStr"/>
+      <c r="D24" s="7" t="n">
+        <v>624123</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>2704646</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>3328769</v>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>108185839</v>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>2027-09</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>108185839</v>
+      </c>
+      <c r="C25" s="4" t="inlineStr"/>
+      <c r="D25" s="5" t="n">
+        <v>608900</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>2704646</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>3313546</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>105481193</v>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>2027-10</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n">
+        <v>105481193</v>
+      </c>
+      <c r="C26" s="6" t="inlineStr"/>
+      <c r="D26" s="7" t="n">
+        <v>593678</v>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>2704646</v>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>3298324</v>
+      </c>
+      <c r="G26" s="7" t="n">
+        <v>102776547</v>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>2027-10</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>102776547</v>
+      </c>
+      <c r="C27" s="4" t="inlineStr"/>
+      <c r="D27" s="5" t="n">
+        <v>578455</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>2704646</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>3283101</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>100071901</v>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>2027-12</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n">
+        <v>100071901</v>
+      </c>
+      <c r="C28" s="6" t="inlineStr"/>
+      <c r="D28" s="7" t="n">
+        <v>563233</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>2704646</v>
+      </c>
+      <c r="F28" s="7" t="n">
+        <v>3267879</v>
+      </c>
+      <c r="G28" s="7" t="n">
+        <v>97367255</v>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>2027-12</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>97367255</v>
+      </c>
+      <c r="C29" s="4" t="inlineStr"/>
+      <c r="D29" s="5" t="n">
+        <v>548010</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>2704646</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>3252656</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>94662609</v>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>2028-01</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="n">
+        <v>94662609</v>
+      </c>
+      <c r="C30" s="6" t="inlineStr"/>
+      <c r="D30" s="7" t="n">
+        <v>532788</v>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>2704646</v>
+      </c>
+      <c r="F30" s="7" t="n">
+        <v>3237434</v>
+      </c>
+      <c r="G30" s="7" t="n">
+        <v>91957963</v>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>2028-03</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>91957963</v>
+      </c>
+      <c r="C31" s="4" t="inlineStr"/>
+      <c r="D31" s="5" t="n">
+        <v>517565</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>2704646</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>3222211</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>89253317</v>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>2028-03</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="n">
+        <v>89253317</v>
+      </c>
+      <c r="C32" s="6" t="inlineStr"/>
+      <c r="D32" s="7" t="n">
+        <v>502343</v>
+      </c>
+      <c r="E32" s="7" t="n">
+        <v>2704646</v>
+      </c>
+      <c r="F32" s="7" t="n">
+        <v>3206989</v>
+      </c>
+      <c r="G32" s="7" t="n">
+        <v>86548671</v>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>2028-05</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>86548671</v>
+      </c>
+      <c r="C33" s="4" t="inlineStr"/>
+      <c r="D33" s="5" t="n">
+        <v>487120</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>2704646</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>3191766</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>83844025</v>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>2028-05</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="n">
+        <v>83844025</v>
+      </c>
+      <c r="C34" s="6" t="inlineStr"/>
+      <c r="D34" s="7" t="n">
+        <v>471898</v>
+      </c>
+      <c r="E34" s="7" t="n">
+        <v>2704646</v>
+      </c>
+      <c r="F34" s="7" t="n">
+        <v>3176544</v>
+      </c>
+      <c r="G34" s="7" t="n">
+        <v>81139379</v>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>2028-07</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>81139379</v>
+      </c>
+      <c r="C35" s="4" t="inlineStr"/>
+      <c r="D35" s="5" t="n">
+        <v>456675</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>2704646</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>3161321</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>78434733</v>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>2028-07</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="n">
+        <v>78434733</v>
+      </c>
+      <c r="C36" s="6" t="inlineStr"/>
+      <c r="D36" s="7" t="n">
+        <v>441453</v>
+      </c>
+      <c r="E36" s="7" t="n">
+        <v>2704646</v>
+      </c>
+      <c r="F36" s="7" t="n">
+        <v>3146099</v>
+      </c>
+      <c r="G36" s="7" t="n">
+        <v>75730087</v>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>2028-08</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>75730087</v>
+      </c>
+      <c r="C37" s="4" t="inlineStr"/>
+      <c r="D37" s="5" t="n">
+        <v>426230</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>2704646</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>3130876</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>73025441</v>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>2028-09</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="n">
+        <v>73025441</v>
+      </c>
+      <c r="C38" s="6" t="inlineStr"/>
+      <c r="D38" s="7" t="n">
+        <v>411008</v>
+      </c>
+      <c r="E38" s="7" t="n">
+        <v>2704646</v>
+      </c>
+      <c r="F38" s="7" t="n">
+        <v>3115654</v>
+      </c>
+      <c r="G38" s="7" t="n">
+        <v>70320795</v>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>2028-10</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>70320795</v>
+      </c>
+      <c r="C39" s="4" t="inlineStr"/>
+      <c r="D39" s="5" t="n">
+        <v>395785</v>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>2704646</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>3100431</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>67616149</v>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>2028-11</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="n">
+        <v>67616149</v>
+      </c>
+      <c r="C40" s="6" t="inlineStr"/>
+      <c r="D40" s="7" t="n">
+        <v>380563</v>
+      </c>
+      <c r="E40" s="7" t="n">
+        <v>2704646</v>
+      </c>
+      <c r="F40" s="7" t="n">
+        <v>3085209</v>
+      </c>
+      <c r="G40" s="7" t="n">
+        <v>64911503</v>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
